--- a/Solver/Max Solver.xlsx
+++ b/Solver/Max Solver.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Solver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C96833EA-955A-45B0-B0CA-5DB3619CEC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671B553B-4CFD-4327-AAE2-D032DBB7E31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{5B0535DC-8105-45F2-975C-D167ECD881EB}"/>
   </bookViews>
@@ -474,61 +474,32 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
       <c r="C2">
         <v>10</v>
-      </c>
-      <c r="D2">
-        <f>B2*C2</f>
-        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>20</v>
-      </c>
       <c r="C3">
         <v>16</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D4" si="0">B3*C3</f>
-        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>230</v>
-      </c>
       <c r="C4">
         <v>33</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>7590</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
-        <f>SUM(B2:B4)</f>
-        <v>350</v>
-      </c>
       <c r="C5" t="s">
         <v>8</v>
-      </c>
-      <c r="D5">
-        <f>SUM(D2:D4)</f>
-        <v>8910</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -576,12 +547,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B13:E13"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
